--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85410764-EF27-46A8-8E7F-9A4D9B3DF082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C606E73F-8F70-401C-B6E7-35F7A5475082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398A0A3D-AE62-4B28-8AB9-1CFDAADF3ED6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398A0A3D-AE62-4B28-8AB9-1CFDAADF3ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ HỌC TẬP (IELTS)</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Trung bình tiến độ học tập thực tế</t>
   </si>
   <si>
+    <t>20/106</t>
+  </si>
+  <si>
     <t>Họ và tên</t>
   </si>
   <si>
@@ -69,35 +72,38 @@
     <t>Trạng Thái</t>
   </si>
   <si>
+    <t>MS3: {0}</t>
+  </si>
+  <si>
+    <t>MS2: {0}</t>
+  </si>
+  <si>
     <t>MS1: {0}</t>
   </si>
   <si>
+    <t>{0}</t>
+  </si>
+  <si>
     <t>Trạng thái: {0}</t>
   </si>
   <si>
-    <t>MS3: {0}</t>
-  </si>
-  <si>
-    <t>MS2: {0}</t>
-  </si>
-  <si>
     <t>Khối: {0}</t>
   </si>
   <si>
     <t>Lớp: {0}</t>
   </si>
   <si>
+    <t>Khóa học: {0}</t>
+  </si>
+  <si>
     <t>Ngày: {0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày: {0} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,22 +122,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -184,30 +174,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -218,43 +184,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top/>
@@ -262,74 +202,114 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -649,144 +629,153 @@
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="28.375" customWidth="1"/>
+    <col min="2" max="2" width="20.125" customWidth="1"/>
     <col min="3" max="3" width="31.875" customWidth="1"/>
     <col min="4" max="4" width="24.625" customWidth="1"/>
     <col min="5" max="5" width="32.375" customWidth="1"/>
-    <col min="6" max="6" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="6" max="6" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
     <col min="10" max="10" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="9" t="s">
-        <v>21</v>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="10"/>
+      <c r="G2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="5"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="3">
+        <v>120</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="11"/>
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ExcelTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C606E73F-8F70-401C-B6E7-35F7A5475082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1714E58A-7318-4F85-8A82-375634EB8D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398A0A3D-AE62-4B28-8AB9-1CFDAADF3ED6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ HỌC TẬP (IELTS)</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>Ngày: {0}</t>
+  </si>
+  <si>
+    <t>UserName</t>
   </si>
 </sst>
 </file>
@@ -273,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -310,6 +313,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -626,22 +632,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749AE6D2-254F-4143-A216-525A397BF871}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.375" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
-    <col min="3" max="3" width="31.875" customWidth="1"/>
-    <col min="4" max="4" width="24.625" customWidth="1"/>
-    <col min="5" max="5" width="32.375" customWidth="1"/>
-    <col min="6" max="6" width="20.625" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
-    <col min="10" max="10" width="22.75" customWidth="1"/>
+    <col min="1" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="20.125" customWidth="1"/>
+    <col min="4" max="4" width="31.875" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="32.375" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.25" customWidth="1"/>
+    <col min="11" max="11" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -653,127 +659,135 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="13"/>
+      <c r="K1" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
+      <c r="B2" s="16"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
+      <c r="B3" s="16"/>
       <c r="C3" s="15"/>
-      <c r="D3" s="3">
+      <c r="D3" s="15"/>
+      <c r="E3" s="3">
         <v>120</v>
       </c>
-      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="3"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ManagerReports/BaoCaoTienDoHocTapIELTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhanPhuc\Fsel\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ManagerReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1714E58A-7318-4F85-8A82-375634EB8D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A940E8-0B23-44FF-A746-B1E82D5D7CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398A0A3D-AE62-4B28-8AB9-1CFDAADF3ED6}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>Trung bình tiến độ học tập thực tế</t>
   </si>
   <si>
-    <t>20/106</t>
-  </si>
-  <si>
     <t>Họ và tên</t>
   </si>
   <si>
@@ -100,6 +97,9 @@
   </si>
   <si>
     <t>UserName</t>
+  </si>
+  <si>
+    <t>0/106</t>
   </si>
 </sst>
 </file>
@@ -116,27 +116,26 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -278,45 +277,43 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,21 +630,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{749AE6D2-254F-4143-A216-525A397BF871}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="31.875" customWidth="1"/>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="32.375" customWidth="1"/>
-    <col min="7" max="7" width="20.625" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
-    <col min="11" max="11" width="22.75" customWidth="1"/>
+    <col min="1" max="2" width="28.375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="20.125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="31.875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="24.625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="32.375" style="14" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="18" style="14" customWidth="1"/>
+    <col min="9" max="9" width="19.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.25" style="14" customWidth="1"/>
+    <col min="11" max="11" width="22.75" style="14" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -660,125 +658,125 @@
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="C6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="3">
-        <v>120</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="15" t="s">
         <v>13</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
